--- a/template/報告書ひな形.xlsx
+++ b/template/報告書ひな形.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frontier-Python\Desktop\個人製作\absence-prediction\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE77A1-3B43-4568-98B9-4A0BE751937B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5733F0A-1F75-4177-973E-73E3A2A9316B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8244" yWindow="552" windowWidth="11868" windowHeight="12816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="696" yWindow="708" windowWidth="11868" windowHeight="12816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -47,10 +47,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>保育園欠席データ分析報告書</t>
-    <phoneticPr fontId="1"/>
-  </si>
   <si>
     <t>〇年〇月〇日</t>
     <rPh sb="1" eb="2">
@@ -198,6 +194,10 @@
   </si>
   <si>
     <t>■ 業務改善提案</t>
+  </si>
+  <si>
+    <t>欠席データ分析報告書</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -530,10 +530,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -833,7 +833,7 @@
     <row r="11" spans="3:28" ht="15" customHeight="1" thickBot="1"/>
     <row r="12" spans="3:28" ht="15" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="44" spans="10:21" ht="15" customHeight="1">
       <c r="J44" s="11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
@@ -1038,7 +1038,7 @@
   <sheetData>
     <row r="2" spans="2:29" ht="15" customHeight="1">
       <c r="B2" s="21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="14" spans="2:29" ht="15" customHeight="1">
       <c r="B14" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -1677,7 +1677,7 @@
   <sheetData>
     <row r="2" spans="2:29" ht="15" customHeight="1">
       <c r="B2" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="5" spans="2:29" ht="15" customHeight="1">
       <c r="B5" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="10" spans="2:29" ht="15" customHeight="1">
       <c r="B10" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="13" spans="2:29" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1">
       <c r="B18" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="21" spans="2:29" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -2312,97 +2312,97 @@
   <sheetData>
     <row r="2" spans="2:29" ht="15" customHeight="1">
       <c r="B2" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+    </row>
+    <row r="3" spans="2:29" ht="15" customHeight="1">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+    </row>
+    <row r="4" spans="2:29" ht="15" customHeight="1">
+      <c r="B4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-    </row>
-    <row r="3" spans="2:29" ht="15" customHeight="1">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-    </row>
-    <row r="4" spans="2:29" ht="15" customHeight="1">
-      <c r="B4" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
     </row>
     <row r="5" spans="2:29" ht="15" customHeight="1">
       <c r="B5" s="32"/>
@@ -2466,512 +2466,512 @@
     </row>
     <row r="7" spans="2:29" ht="15" customHeight="1">
       <c r="B7" s="36"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
       <c r="AC7" s="37"/>
     </row>
     <row r="8" spans="2:29" ht="15" customHeight="1">
       <c r="B8" s="36"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
       <c r="AC8" s="37"/>
     </row>
     <row r="9" spans="2:29" ht="15" customHeight="1">
       <c r="B9" s="36"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
       <c r="AC9" s="37"/>
     </row>
     <row r="10" spans="2:29" ht="15" customHeight="1">
       <c r="B10" s="36"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
       <c r="AC10" s="37"/>
     </row>
     <row r="11" spans="2:29" ht="15" customHeight="1">
       <c r="B11" s="36"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
       <c r="AC11" s="37"/>
     </row>
     <row r="12" spans="2:29" ht="15" customHeight="1">
       <c r="B12" s="36"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
       <c r="AC12" s="37"/>
     </row>
     <row r="13" spans="2:29" ht="15" customHeight="1">
       <c r="B13" s="36"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
       <c r="AC13" s="37"/>
     </row>
     <row r="14" spans="2:29" ht="15" customHeight="1">
       <c r="B14" s="36"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
       <c r="AC14" s="37"/>
     </row>
     <row r="15" spans="2:29" ht="15" customHeight="1">
       <c r="B15" s="36"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31"/>
       <c r="AC15" s="37"/>
     </row>
     <row r="16" spans="2:29" ht="15" customHeight="1">
       <c r="B16" s="36"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
       <c r="AC16" s="37"/>
     </row>
     <row r="17" spans="2:29" ht="15" customHeight="1">
       <c r="B17" s="36"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
       <c r="AC17" s="37"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1">
       <c r="B18" s="36"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
       <c r="AC18" s="37"/>
     </row>
     <row r="19" spans="2:29" ht="15" customHeight="1">
       <c r="B19" s="36"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="31"/>
       <c r="AC19" s="37"/>
     </row>
     <row r="20" spans="2:29" ht="15" customHeight="1">
       <c r="B20" s="36"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
       <c r="AC20" s="37"/>
     </row>
     <row r="21" spans="2:29" ht="15" customHeight="1">
       <c r="B21" s="36"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
-      <c r="AA21" s="30"/>
-      <c r="AB21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="31"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="31"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="31"/>
+      <c r="AB21" s="31"/>
       <c r="AC21" s="37"/>
     </row>
     <row r="22" spans="2:29" ht="15" customHeight="1">
       <c r="B22" s="36"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
       <c r="AC22" s="37"/>
     </row>
     <row r="23" spans="2:29" ht="15" customHeight="1">
       <c r="B23" s="36"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
       <c r="AC23" s="37"/>
     </row>
     <row r="24" spans="2:29" ht="15" customHeight="1">
@@ -3005,36 +3005,36 @@
       <c r="AC24" s="39"/>
     </row>
     <row r="25" spans="2:29" ht="15" customHeight="1">
-      <c r="B25" s="31" t="s">
-        <v>19</v>
+      <c r="B25" s="30" t="s">
+        <v>18</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="31"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
+      <c r="AC25" s="31"/>
     </row>
     <row r="26" spans="2:29" ht="15" customHeight="1">
       <c r="B26" s="32"/>
@@ -3098,212 +3098,212 @@
     </row>
     <row r="28" spans="2:29" ht="15" customHeight="1">
       <c r="B28" s="36"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
       <c r="AC28" s="37"/>
     </row>
     <row r="29" spans="2:29" ht="15" customHeight="1">
       <c r="B29" s="36"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
       <c r="AC29" s="37"/>
     </row>
     <row r="30" spans="2:29" ht="15" customHeight="1">
       <c r="B30" s="36"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="31"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
       <c r="AC30" s="37"/>
     </row>
     <row r="31" spans="2:29" ht="15" customHeight="1">
       <c r="B31" s="36"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
       <c r="AC31" s="37"/>
     </row>
     <row r="32" spans="2:29" ht="15" customHeight="1">
       <c r="B32" s="36"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
       <c r="AC32" s="37"/>
     </row>
     <row r="33" spans="2:29" ht="15" customHeight="1">
       <c r="B33" s="36"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="31"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="31"/>
+      <c r="AB33" s="31"/>
       <c r="AC33" s="37"/>
     </row>
     <row r="34" spans="2:29" ht="15" customHeight="1">
       <c r="B34" s="36"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
       <c r="AC34" s="37"/>
     </row>
     <row r="35" spans="2:29" ht="15" customHeight="1">
@@ -3337,36 +3337,36 @@
       <c r="AC35" s="39"/>
     </row>
     <row r="37" spans="2:29" ht="15" customHeight="1">
-      <c r="B37" s="31" t="s">
-        <v>20</v>
+      <c r="B37" s="30" t="s">
+        <v>19</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
     </row>
     <row r="38" spans="2:29" ht="15" customHeight="1">
       <c r="B38" s="32"/>
@@ -3430,212 +3430,212 @@
     </row>
     <row r="40" spans="2:29" ht="15" customHeight="1">
       <c r="B40" s="36"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
       <c r="AC40" s="37"/>
     </row>
     <row r="41" spans="2:29" ht="15" customHeight="1">
       <c r="B41" s="36"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
-      <c r="R41" s="30"/>
-      <c r="S41" s="30"/>
-      <c r="T41" s="30"/>
-      <c r="U41" s="30"/>
-      <c r="V41" s="30"/>
-      <c r="W41" s="30"/>
-      <c r="X41" s="30"/>
-      <c r="Y41" s="30"/>
-      <c r="Z41" s="30"/>
-      <c r="AA41" s="30"/>
-      <c r="AB41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="31"/>
+      <c r="S41" s="31"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="31"/>
+      <c r="Y41" s="31"/>
+      <c r="Z41" s="31"/>
+      <c r="AA41" s="31"/>
+      <c r="AB41" s="31"/>
       <c r="AC41" s="37"/>
     </row>
     <row r="42" spans="2:29" ht="15" customHeight="1">
       <c r="B42" s="36"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
-      <c r="W42" s="30"/>
-      <c r="X42" s="30"/>
-      <c r="Y42" s="30"/>
-      <c r="Z42" s="30"/>
-      <c r="AA42" s="30"/>
-      <c r="AB42" s="30"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="31"/>
+      <c r="Y42" s="31"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
       <c r="AC42" s="37"/>
     </row>
     <row r="43" spans="2:29" ht="15" customHeight="1">
       <c r="B43" s="36"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
       <c r="AC43" s="37"/>
     </row>
     <row r="44" spans="2:29" ht="15" customHeight="1">
       <c r="B44" s="36"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="30"/>
-      <c r="S44" s="30"/>
-      <c r="T44" s="30"/>
-      <c r="U44" s="30"/>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
-      <c r="X44" s="30"/>
-      <c r="Y44" s="30"/>
-      <c r="Z44" s="30"/>
-      <c r="AA44" s="30"/>
-      <c r="AB44" s="30"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="31"/>
+      <c r="S44" s="31"/>
+      <c r="T44" s="31"/>
+      <c r="U44" s="31"/>
+      <c r="V44" s="31"/>
+      <c r="W44" s="31"/>
+      <c r="X44" s="31"/>
+      <c r="Y44" s="31"/>
+      <c r="Z44" s="31"/>
+      <c r="AA44" s="31"/>
+      <c r="AB44" s="31"/>
       <c r="AC44" s="37"/>
     </row>
     <row r="45" spans="2:29" ht="15" customHeight="1">
       <c r="B45" s="36"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="30"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
-      <c r="X45" s="30"/>
-      <c r="Y45" s="30"/>
-      <c r="Z45" s="30"/>
-      <c r="AA45" s="30"/>
-      <c r="AB45" s="30"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="31"/>
+      <c r="S45" s="31"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
+      <c r="W45" s="31"/>
+      <c r="X45" s="31"/>
+      <c r="Y45" s="31"/>
+      <c r="Z45" s="31"/>
+      <c r="AA45" s="31"/>
+      <c r="AB45" s="31"/>
       <c r="AC45" s="37"/>
     </row>
     <row r="46" spans="2:29" ht="15" customHeight="1">
       <c r="B46" s="36"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
+      <c r="Y46" s="31"/>
+      <c r="Z46" s="31"/>
+      <c r="AA46" s="31"/>
+      <c r="AB46" s="31"/>
       <c r="AC46" s="37"/>
     </row>
     <row r="47" spans="2:29" ht="15" customHeight="1">
@@ -3694,150 +3694,7 @@
   <sheetData>
     <row r="2" spans="2:29" ht="15" customHeight="1">
       <c r="B2" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-    </row>
-    <row r="3" spans="2:29" ht="15" customHeight="1">
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-    </row>
-    <row r="25" spans="2:29" ht="15" customHeight="1">
-      <c r="B25" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-    </row>
-    <row r="26" spans="2:29" ht="15" customHeight="1">
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:AC3"/>
-    <mergeCell ref="B25:AC26"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11169EB4-EDDA-48A8-A4D1-F5AA21A1A876}">
-  <dimension ref="B2:AC26"/>
-  <sheetFormatPr defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="16384" width="2.59765625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:29" ht="15" customHeight="1">
-      <c r="B2" s="21" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -3970,152 +3827,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{384DEDF8-0BCA-4E13-B586-FAC223EF30EA}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11169EB4-EDDA-48A8-A4D1-F5AA21A1A876}">
   <dimension ref="B2:AC26"/>
-  <sheetFormatPr defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="16384" width="2.59765625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:29" ht="15" customHeight="1">
-      <c r="B2" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-    </row>
-    <row r="3" spans="2:29" ht="15" customHeight="1">
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-    </row>
-    <row r="25" spans="2:29" ht="15" customHeight="1">
-      <c r="B25" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-    </row>
-    <row r="26" spans="2:29" ht="15" customHeight="1">
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:AC3"/>
-    <mergeCell ref="B25:AC26"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B88A5D-89F1-4270-A475-9335C7982824}">
-  <dimension ref="B2:AC3"/>
   <sheetFormatPr defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="2.59765625" style="1"/>
@@ -4183,6 +3897,292 @@
       <c r="AB3" s="21"/>
       <c r="AC3" s="21"/>
     </row>
+    <row r="25" spans="2:29" ht="15" customHeight="1">
+      <c r="B25" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+      <c r="AB25" s="21"/>
+      <c r="AC25" s="21"/>
+    </row>
+    <row r="26" spans="2:29" ht="15" customHeight="1">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+      <c r="AB26" s="21"/>
+      <c r="AC26" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:AC3"/>
+    <mergeCell ref="B25:AC26"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{384DEDF8-0BCA-4E13-B586-FAC223EF30EA}">
+  <dimension ref="B2:AC26"/>
+  <sheetFormatPr defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="2.59765625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:29" ht="15" customHeight="1">
+      <c r="B2" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+    </row>
+    <row r="3" spans="2:29" ht="15" customHeight="1">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+    </row>
+    <row r="25" spans="2:29" ht="15" customHeight="1">
+      <c r="B25" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+      <c r="AB25" s="21"/>
+      <c r="AC25" s="21"/>
+    </row>
+    <row r="26" spans="2:29" ht="15" customHeight="1">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+      <c r="AB26" s="21"/>
+      <c r="AC26" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:AC3"/>
+    <mergeCell ref="B25:AC26"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B88A5D-89F1-4270-A475-9335C7982824}">
+  <dimension ref="B2:AC3"/>
+  <sheetFormatPr defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="2.59765625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:29" ht="15" customHeight="1">
+      <c r="B2" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+    </row>
+    <row r="3" spans="2:29" ht="15" customHeight="1">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:AC3"/>
@@ -4203,97 +4203,97 @@
   <sheetData>
     <row r="2" spans="2:29" ht="15" customHeight="1">
       <c r="B2" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+    </row>
+    <row r="3" spans="2:29" ht="15" customHeight="1">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+    </row>
+    <row r="4" spans="2:29" ht="15" customHeight="1">
+      <c r="B4" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-    </row>
-    <row r="3" spans="2:29" ht="15" customHeight="1">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-    </row>
-    <row r="4" spans="2:29" ht="15" customHeight="1">
-      <c r="B4" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
     </row>
     <row r="5" spans="2:29" ht="15" customHeight="1">
       <c r="B5" s="32"/>
@@ -4357,512 +4357,512 @@
     </row>
     <row r="7" spans="2:29" ht="15" customHeight="1">
       <c r="B7" s="36"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
       <c r="AC7" s="37"/>
     </row>
     <row r="8" spans="2:29" ht="15" customHeight="1">
       <c r="B8" s="36"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
       <c r="AC8" s="37"/>
     </row>
     <row r="9" spans="2:29" ht="15" customHeight="1">
       <c r="B9" s="36"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
       <c r="AC9" s="37"/>
     </row>
     <row r="10" spans="2:29" ht="15" customHeight="1">
       <c r="B10" s="36"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
       <c r="AC10" s="37"/>
     </row>
     <row r="11" spans="2:29" ht="15" customHeight="1">
       <c r="B11" s="36"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
       <c r="AC11" s="37"/>
     </row>
     <row r="12" spans="2:29" ht="15" customHeight="1">
       <c r="B12" s="36"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
       <c r="AC12" s="37"/>
     </row>
     <row r="13" spans="2:29" ht="15" customHeight="1">
       <c r="B13" s="36"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
       <c r="AC13" s="37"/>
     </row>
     <row r="14" spans="2:29" ht="15" customHeight="1">
       <c r="B14" s="36"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
       <c r="AC14" s="37"/>
     </row>
     <row r="15" spans="2:29" ht="15" customHeight="1">
       <c r="B15" s="36"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31"/>
       <c r="AC15" s="37"/>
     </row>
     <row r="16" spans="2:29" ht="15" customHeight="1">
       <c r="B16" s="36"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
       <c r="AC16" s="37"/>
     </row>
     <row r="17" spans="2:29" ht="15" customHeight="1">
       <c r="B17" s="36"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
       <c r="AC17" s="37"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1">
       <c r="B18" s="36"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
       <c r="AC18" s="37"/>
     </row>
     <row r="19" spans="2:29" ht="15" customHeight="1">
       <c r="B19" s="36"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="31"/>
       <c r="AC19" s="37"/>
     </row>
     <row r="20" spans="2:29" ht="15" customHeight="1">
       <c r="B20" s="36"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
       <c r="AC20" s="37"/>
     </row>
     <row r="21" spans="2:29" ht="15" customHeight="1">
       <c r="B21" s="36"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
-      <c r="AA21" s="30"/>
-      <c r="AB21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="31"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="31"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="31"/>
+      <c r="AB21" s="31"/>
       <c r="AC21" s="37"/>
     </row>
     <row r="22" spans="2:29" ht="15" customHeight="1">
       <c r="B22" s="36"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
       <c r="AC22" s="37"/>
     </row>
     <row r="23" spans="2:29" ht="15" customHeight="1">
       <c r="B23" s="36"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
       <c r="AC23" s="37"/>
     </row>
     <row r="24" spans="2:29" ht="15" customHeight="1">
@@ -4896,36 +4896,36 @@
       <c r="AC24" s="39"/>
     </row>
     <row r="26" spans="2:29" ht="15" customHeight="1">
-      <c r="B26" s="31" t="s">
-        <v>23</v>
+      <c r="B26" s="30" t="s">
+        <v>22</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
     </row>
     <row r="27" spans="2:29" ht="15" customHeight="1">
       <c r="B27" s="32"/>
@@ -4989,482 +4989,482 @@
     </row>
     <row r="29" spans="2:29" ht="15" customHeight="1">
       <c r="B29" s="36"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
       <c r="AC29" s="37"/>
     </row>
     <row r="30" spans="2:29" ht="15" customHeight="1">
       <c r="B30" s="36"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="31"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
       <c r="AC30" s="37"/>
     </row>
     <row r="31" spans="2:29" ht="15" customHeight="1">
       <c r="B31" s="36"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
       <c r="AC31" s="37"/>
     </row>
     <row r="32" spans="2:29" ht="15" customHeight="1">
       <c r="B32" s="36"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
       <c r="AC32" s="37"/>
     </row>
     <row r="33" spans="2:29" ht="15" customHeight="1">
       <c r="B33" s="36"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="31"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="31"/>
+      <c r="AB33" s="31"/>
       <c r="AC33" s="37"/>
     </row>
     <row r="34" spans="2:29" ht="15" customHeight="1">
       <c r="B34" s="36"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
       <c r="AC34" s="37"/>
     </row>
     <row r="35" spans="2:29" ht="15" customHeight="1">
       <c r="B35" s="36"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="30"/>
-      <c r="S35" s="30"/>
-      <c r="T35" s="30"/>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="31"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="31"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="31"/>
+      <c r="Y35" s="31"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="31"/>
+      <c r="AB35" s="31"/>
       <c r="AC35" s="37"/>
     </row>
     <row r="36" spans="2:29" ht="15" customHeight="1">
       <c r="B36" s="36"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="30"/>
-      <c r="O36" s="30"/>
-      <c r="P36" s="30"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
-      <c r="S36" s="30"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="30"/>
-      <c r="V36" s="30"/>
-      <c r="W36" s="30"/>
-      <c r="X36" s="30"/>
-      <c r="Y36" s="30"/>
-      <c r="Z36" s="30"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="30"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="31"/>
+      <c r="S36" s="31"/>
+      <c r="T36" s="31"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="31"/>
+      <c r="Y36" s="31"/>
+      <c r="Z36" s="31"/>
+      <c r="AA36" s="31"/>
+      <c r="AB36" s="31"/>
       <c r="AC36" s="37"/>
     </row>
     <row r="37" spans="2:29" ht="15" customHeight="1">
       <c r="B37" s="36"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="31"/>
       <c r="AC37" s="37"/>
     </row>
     <row r="38" spans="2:29" ht="15" customHeight="1">
       <c r="B38" s="36"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="30"/>
-      <c r="S38" s="30"/>
-      <c r="T38" s="30"/>
-      <c r="U38" s="30"/>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
-      <c r="X38" s="30"/>
-      <c r="Y38" s="30"/>
-      <c r="Z38" s="30"/>
-      <c r="AA38" s="30"/>
-      <c r="AB38" s="30"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="31"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="31"/>
+      <c r="S38" s="31"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="31"/>
+      <c r="V38" s="31"/>
+      <c r="W38" s="31"/>
+      <c r="X38" s="31"/>
+      <c r="Y38" s="31"/>
+      <c r="Z38" s="31"/>
+      <c r="AA38" s="31"/>
+      <c r="AB38" s="31"/>
       <c r="AC38" s="37"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1">
       <c r="B39" s="36"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
-      <c r="S39" s="30"/>
-      <c r="T39" s="30"/>
-      <c r="U39" s="30"/>
-      <c r="V39" s="30"/>
-      <c r="W39" s="30"/>
-      <c r="X39" s="30"/>
-      <c r="Y39" s="30"/>
-      <c r="Z39" s="30"/>
-      <c r="AA39" s="30"/>
-      <c r="AB39" s="30"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="31"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="31"/>
+      <c r="S39" s="31"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="31"/>
+      <c r="V39" s="31"/>
+      <c r="W39" s="31"/>
+      <c r="X39" s="31"/>
+      <c r="Y39" s="31"/>
+      <c r="Z39" s="31"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
       <c r="AC39" s="37"/>
     </row>
     <row r="40" spans="2:29" ht="15" customHeight="1">
       <c r="B40" s="36"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
       <c r="AC40" s="37"/>
     </row>
     <row r="41" spans="2:29" ht="15" customHeight="1">
       <c r="B41" s="36"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
-      <c r="R41" s="30"/>
-      <c r="S41" s="30"/>
-      <c r="T41" s="30"/>
-      <c r="U41" s="30"/>
-      <c r="V41" s="30"/>
-      <c r="W41" s="30"/>
-      <c r="X41" s="30"/>
-      <c r="Y41" s="30"/>
-      <c r="Z41" s="30"/>
-      <c r="AA41" s="30"/>
-      <c r="AB41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="31"/>
+      <c r="S41" s="31"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="31"/>
+      <c r="Y41" s="31"/>
+      <c r="Z41" s="31"/>
+      <c r="AA41" s="31"/>
+      <c r="AB41" s="31"/>
       <c r="AC41" s="37"/>
     </row>
     <row r="42" spans="2:29" ht="15" customHeight="1">
       <c r="B42" s="36"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
-      <c r="W42" s="30"/>
-      <c r="X42" s="30"/>
-      <c r="Y42" s="30"/>
-      <c r="Z42" s="30"/>
-      <c r="AA42" s="30"/>
-      <c r="AB42" s="30"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="31"/>
+      <c r="Y42" s="31"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
       <c r="AC42" s="37"/>
     </row>
     <row r="43" spans="2:29" ht="15" customHeight="1">
       <c r="B43" s="36"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
       <c r="AC43" s="37"/>
     </row>
     <row r="44" spans="2:29" ht="15" customHeight="1">
       <c r="B44" s="36"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="30"/>
-      <c r="S44" s="30"/>
-      <c r="T44" s="30"/>
-      <c r="U44" s="30"/>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
-      <c r="X44" s="30"/>
-      <c r="Y44" s="30"/>
-      <c r="Z44" s="30"/>
-      <c r="AA44" s="30"/>
-      <c r="AB44" s="30"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="31"/>
+      <c r="S44" s="31"/>
+      <c r="T44" s="31"/>
+      <c r="U44" s="31"/>
+      <c r="V44" s="31"/>
+      <c r="W44" s="31"/>
+      <c r="X44" s="31"/>
+      <c r="Y44" s="31"/>
+      <c r="Z44" s="31"/>
+      <c r="AA44" s="31"/>
+      <c r="AB44" s="31"/>
       <c r="AC44" s="37"/>
     </row>
     <row r="45" spans="2:29" ht="15" customHeight="1">

--- a/template/報告書ひな形.xlsx
+++ b/template/報告書ひな形.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frontier-Python\Desktop\個人製作\absence-prediction\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8675312-6925-4F03-A008-E134CBE714C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2169CE6-79A8-4088-ADA2-0625E1F20F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="108" windowWidth="9708" windowHeight="12816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'1'!$A$1:$AE$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2'!$A$1:$AE$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2'!$A$1:$AE$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3'!$A$1:$AE$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'4'!$A$1:$AE$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'5'!$A$1:$AE$47</definedName>
@@ -528,10 +528,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1663,7 +1663,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C66FE0-4EA8-4942-A5A4-832E55B0C149}">
-  <dimension ref="B2:AC51"/>
+  <dimension ref="B2:AC54"/>
   <sheetFormatPr defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="2.59765625" style="1"/>
@@ -1673,95 +1673,95 @@
       <c r="B2" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
     </row>
     <row r="3" spans="2:29" ht="15" customHeight="1">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
     </row>
     <row r="4" spans="2:29" ht="15" customHeight="1">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
     </row>
     <row r="5" spans="2:29" ht="15" customHeight="1">
       <c r="B5" s="32"/>
@@ -1825,812 +1825,812 @@
     </row>
     <row r="7" spans="2:29" ht="15" customHeight="1">
       <c r="B7" s="36"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
       <c r="AC7" s="37"/>
     </row>
     <row r="8" spans="2:29" ht="15" customHeight="1">
       <c r="B8" s="36"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
       <c r="AC8" s="37"/>
     </row>
     <row r="9" spans="2:29" ht="15" customHeight="1">
       <c r="B9" s="36"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
       <c r="AC9" s="37"/>
     </row>
     <row r="10" spans="2:29" ht="15" customHeight="1">
       <c r="B10" s="36"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
       <c r="AC10" s="37"/>
     </row>
     <row r="11" spans="2:29" ht="15" customHeight="1">
       <c r="B11" s="36"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
       <c r="AC11" s="37"/>
     </row>
     <row r="12" spans="2:29" ht="15" customHeight="1">
       <c r="B12" s="36"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
       <c r="AC12" s="37"/>
     </row>
     <row r="13" spans="2:29" ht="15" customHeight="1">
       <c r="B13" s="36"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
       <c r="AC13" s="37"/>
     </row>
     <row r="14" spans="2:29" ht="15" customHeight="1">
       <c r="B14" s="36"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
       <c r="AC14" s="37"/>
     </row>
     <row r="15" spans="2:29" ht="15" customHeight="1">
       <c r="B15" s="36"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31"/>
       <c r="AC15" s="37"/>
     </row>
     <row r="16" spans="2:29" ht="15" customHeight="1">
       <c r="B16" s="36"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
       <c r="AC16" s="37"/>
     </row>
     <row r="17" spans="2:29" ht="15" customHeight="1">
       <c r="B17" s="36"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
       <c r="AC17" s="37"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1">
       <c r="B18" s="36"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
       <c r="AC18" s="37"/>
     </row>
     <row r="19" spans="2:29" ht="15" customHeight="1">
       <c r="B19" s="36"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="31"/>
       <c r="AC19" s="37"/>
     </row>
     <row r="20" spans="2:29" ht="15" customHeight="1">
       <c r="B20" s="36"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
       <c r="AC20" s="37"/>
     </row>
     <row r="21" spans="2:29" ht="15" customHeight="1">
       <c r="B21" s="36"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
-      <c r="AA21" s="30"/>
-      <c r="AB21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="31"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="31"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="31"/>
+      <c r="AB21" s="31"/>
       <c r="AC21" s="37"/>
     </row>
     <row r="22" spans="2:29" ht="15" customHeight="1">
       <c r="B22" s="36"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
       <c r="AC22" s="37"/>
     </row>
     <row r="23" spans="2:29" ht="15" customHeight="1">
       <c r="B23" s="36"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
       <c r="AC23" s="37"/>
     </row>
     <row r="24" spans="2:29" ht="15" customHeight="1">
       <c r="B24" s="36"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="31"/>
       <c r="AC24" s="37"/>
     </row>
     <row r="25" spans="2:29" ht="15" customHeight="1">
       <c r="B25" s="36"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="31"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
       <c r="AC25" s="37"/>
     </row>
     <row r="26" spans="2:29" ht="15" customHeight="1">
       <c r="B26" s="36"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
       <c r="AC26" s="37"/>
     </row>
     <row r="27" spans="2:29" ht="15" customHeight="1">
       <c r="B27" s="36"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="31"/>
       <c r="AC27" s="37"/>
     </row>
     <row r="28" spans="2:29" ht="15" customHeight="1">
       <c r="B28" s="36"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
       <c r="AC28" s="37"/>
     </row>
     <row r="29" spans="2:29" ht="15" customHeight="1">
       <c r="B29" s="36"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
       <c r="AC29" s="37"/>
     </row>
     <row r="30" spans="2:29" ht="15" customHeight="1">
       <c r="B30" s="36"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="31"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
       <c r="AC30" s="37"/>
     </row>
     <row r="31" spans="2:29" ht="15" customHeight="1">
       <c r="B31" s="36"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
       <c r="AC31" s="37"/>
     </row>
     <row r="32" spans="2:29" ht="15" customHeight="1">
       <c r="B32" s="36"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
       <c r="AC32" s="37"/>
     </row>
     <row r="33" spans="2:29" ht="15" customHeight="1">
       <c r="B33" s="36"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="31"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="31"/>
+      <c r="AB33" s="31"/>
       <c r="AC33" s="37"/>
     </row>
     <row r="34" spans="2:29" ht="15" customHeight="1">
@@ -2664,36 +2664,36 @@
       <c r="AC34" s="39"/>
     </row>
     <row r="35" spans="2:29" ht="15" customHeight="1">
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="30"/>
-      <c r="S35" s="30"/>
-      <c r="T35" s="30"/>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
-      <c r="AC35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="31"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="31"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="31"/>
+      <c r="Y35" s="31"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="31"/>
+      <c r="AB35" s="31"/>
+      <c r="AC35" s="31"/>
     </row>
     <row r="36" spans="2:29" ht="15" customHeight="1">
       <c r="B36" s="32"/>
@@ -2757,439 +2757,529 @@
     </row>
     <row r="38" spans="2:29" ht="15" customHeight="1">
       <c r="B38" s="36"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="30"/>
-      <c r="S38" s="30"/>
-      <c r="T38" s="30"/>
-      <c r="U38" s="30"/>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
-      <c r="X38" s="30"/>
-      <c r="Y38" s="30"/>
-      <c r="Z38" s="30"/>
-      <c r="AA38" s="30"/>
-      <c r="AB38" s="30"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="31"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="31"/>
+      <c r="S38" s="31"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="31"/>
+      <c r="V38" s="31"/>
+      <c r="W38" s="31"/>
+      <c r="X38" s="31"/>
+      <c r="Y38" s="31"/>
+      <c r="Z38" s="31"/>
+      <c r="AA38" s="31"/>
+      <c r="AB38" s="31"/>
       <c r="AC38" s="37"/>
     </row>
     <row r="39" spans="2:29" ht="15" customHeight="1">
       <c r="B39" s="36"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
-      <c r="S39" s="30"/>
-      <c r="T39" s="30"/>
-      <c r="U39" s="30"/>
-      <c r="V39" s="30"/>
-      <c r="W39" s="30"/>
-      <c r="X39" s="30"/>
-      <c r="Y39" s="30"/>
-      <c r="Z39" s="30"/>
-      <c r="AA39" s="30"/>
-      <c r="AB39" s="30"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="31"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="31"/>
+      <c r="S39" s="31"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="31"/>
+      <c r="V39" s="31"/>
+      <c r="W39" s="31"/>
+      <c r="X39" s="31"/>
+      <c r="Y39" s="31"/>
+      <c r="Z39" s="31"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
       <c r="AC39" s="37"/>
     </row>
     <row r="40" spans="2:29" ht="15" customHeight="1">
       <c r="B40" s="36"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
       <c r="AC40" s="37"/>
     </row>
     <row r="41" spans="2:29" ht="15" customHeight="1">
-      <c r="B41" s="38"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="32"/>
-      <c r="O41" s="32"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="32"/>
-      <c r="R41" s="32"/>
-      <c r="S41" s="32"/>
-      <c r="T41" s="32"/>
-      <c r="U41" s="32"/>
-      <c r="V41" s="32"/>
-      <c r="W41" s="32"/>
-      <c r="X41" s="32"/>
-      <c r="Y41" s="32"/>
-      <c r="Z41" s="32"/>
-      <c r="AA41" s="32"/>
-      <c r="AB41" s="32"/>
-      <c r="AC41" s="39"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="31"/>
+      <c r="S41" s="31"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="31"/>
+      <c r="Y41" s="31"/>
+      <c r="Z41" s="31"/>
+      <c r="AA41" s="31"/>
+      <c r="AB41" s="31"/>
+      <c r="AC41" s="37"/>
     </row>
     <row r="42" spans="2:29" ht="15" customHeight="1">
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="36"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="31"/>
+      <c r="Y42" s="31"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
+      <c r="AC42" s="37"/>
+    </row>
+    <row r="43" spans="2:29" ht="15" customHeight="1">
+      <c r="B43" s="36"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
+      <c r="AC43" s="37"/>
+    </row>
+    <row r="44" spans="2:29" ht="15" customHeight="1">
+      <c r="B44" s="38"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32"/>
+      <c r="T44" s="32"/>
+      <c r="U44" s="32"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="32"/>
+      <c r="X44" s="32"/>
+      <c r="Y44" s="32"/>
+      <c r="Z44" s="32"/>
+      <c r="AA44" s="32"/>
+      <c r="AB44" s="32"/>
+      <c r="AC44" s="39"/>
+    </row>
+    <row r="45" spans="2:29" ht="15" customHeight="1">
+      <c r="B45" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
-      <c r="W42" s="30"/>
-      <c r="X42" s="30"/>
-      <c r="Y42" s="30"/>
-      <c r="Z42" s="30"/>
-      <c r="AA42" s="30"/>
-      <c r="AB42" s="30"/>
-      <c r="AC42" s="30"/>
-    </row>
-    <row r="43" spans="2:29" ht="15" customHeight="1">
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="32"/>
-      <c r="R43" s="32"/>
-      <c r="S43" s="32"/>
-      <c r="T43" s="32"/>
-      <c r="U43" s="32"/>
-      <c r="V43" s="32"/>
-      <c r="W43" s="32"/>
-      <c r="X43" s="32"/>
-      <c r="Y43" s="32"/>
-      <c r="Z43" s="32"/>
-      <c r="AA43" s="32"/>
-      <c r="AB43" s="32"/>
-      <c r="AC43" s="32"/>
-    </row>
-    <row r="44" spans="2:29" ht="15" customHeight="1">
-      <c r="B44" s="33"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="34"/>
-      <c r="N44" s="34"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="34"/>
-      <c r="W44" s="34"/>
-      <c r="X44" s="34"/>
-      <c r="Y44" s="34"/>
-      <c r="Z44" s="34"/>
-      <c r="AA44" s="34"/>
-      <c r="AB44" s="34"/>
-      <c r="AC44" s="35"/>
-    </row>
-    <row r="45" spans="2:29" ht="15" customHeight="1">
-      <c r="B45" s="36"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="30"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
-      <c r="X45" s="30"/>
-      <c r="Y45" s="30"/>
-      <c r="Z45" s="30"/>
-      <c r="AA45" s="30"/>
-      <c r="AB45" s="30"/>
-      <c r="AC45" s="37"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="31"/>
+      <c r="S45" s="31"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
+      <c r="W45" s="31"/>
+      <c r="X45" s="31"/>
+      <c r="Y45" s="31"/>
+      <c r="Z45" s="31"/>
+      <c r="AA45" s="31"/>
+      <c r="AB45" s="31"/>
+      <c r="AC45" s="31"/>
     </row>
     <row r="46" spans="2:29" ht="15" customHeight="1">
-      <c r="B46" s="36"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="37"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="32"/>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+      <c r="Z46" s="32"/>
+      <c r="AA46" s="32"/>
+      <c r="AB46" s="32"/>
+      <c r="AC46" s="32"/>
     </row>
     <row r="47" spans="2:29" ht="15" customHeight="1">
-      <c r="B47" s="36"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="30"/>
-      <c r="S47" s="30"/>
-      <c r="T47" s="30"/>
-      <c r="U47" s="30"/>
-      <c r="V47" s="30"/>
-      <c r="W47" s="30"/>
-      <c r="X47" s="30"/>
-      <c r="Y47" s="30"/>
-      <c r="Z47" s="30"/>
-      <c r="AA47" s="30"/>
-      <c r="AB47" s="30"/>
-      <c r="AC47" s="37"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
+      <c r="N47" s="34"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="34"/>
+      <c r="Q47" s="34"/>
+      <c r="R47" s="34"/>
+      <c r="S47" s="34"/>
+      <c r="T47" s="34"/>
+      <c r="U47" s="34"/>
+      <c r="V47" s="34"/>
+      <c r="W47" s="34"/>
+      <c r="X47" s="34"/>
+      <c r="Y47" s="34"/>
+      <c r="Z47" s="34"/>
+      <c r="AA47" s="34"/>
+      <c r="AB47" s="34"/>
+      <c r="AC47" s="35"/>
     </row>
     <row r="48" spans="2:29" ht="15" customHeight="1">
       <c r="B48" s="36"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="30"/>
-      <c r="S48" s="30"/>
-      <c r="T48" s="30"/>
-      <c r="U48" s="30"/>
-      <c r="V48" s="30"/>
-      <c r="W48" s="30"/>
-      <c r="X48" s="30"/>
-      <c r="Y48" s="30"/>
-      <c r="Z48" s="30"/>
-      <c r="AA48" s="30"/>
-      <c r="AB48" s="30"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="31"/>
+      <c r="T48" s="31"/>
+      <c r="U48" s="31"/>
+      <c r="V48" s="31"/>
+      <c r="W48" s="31"/>
+      <c r="X48" s="31"/>
+      <c r="Y48" s="31"/>
+      <c r="Z48" s="31"/>
+      <c r="AA48" s="31"/>
+      <c r="AB48" s="31"/>
       <c r="AC48" s="37"/>
     </row>
     <row r="49" spans="2:29" ht="15" customHeight="1">
       <c r="B49" s="36"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
+      <c r="Y49" s="31"/>
+      <c r="Z49" s="31"/>
+      <c r="AA49" s="31"/>
+      <c r="AB49" s="31"/>
       <c r="AC49" s="37"/>
     </row>
     <row r="50" spans="2:29" ht="15" customHeight="1">
       <c r="B50" s="36"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="30"/>
-      <c r="K50" s="30"/>
-      <c r="L50" s="30"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="30"/>
-      <c r="O50" s="30"/>
-      <c r="P50" s="30"/>
-      <c r="Q50" s="30"/>
-      <c r="R50" s="30"/>
-      <c r="S50" s="30"/>
-      <c r="T50" s="30"/>
-      <c r="U50" s="30"/>
-      <c r="V50" s="30"/>
-      <c r="W50" s="30"/>
-      <c r="X50" s="30"/>
-      <c r="Y50" s="30"/>
-      <c r="Z50" s="30"/>
-      <c r="AA50" s="30"/>
-      <c r="AB50" s="30"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="31"/>
+      <c r="K50" s="31"/>
+      <c r="L50" s="31"/>
+      <c r="M50" s="31"/>
+      <c r="N50" s="31"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="31"/>
+      <c r="Q50" s="31"/>
+      <c r="R50" s="31"/>
+      <c r="S50" s="31"/>
+      <c r="T50" s="31"/>
+      <c r="U50" s="31"/>
+      <c r="V50" s="31"/>
+      <c r="W50" s="31"/>
+      <c r="X50" s="31"/>
+      <c r="Y50" s="31"/>
+      <c r="Z50" s="31"/>
+      <c r="AA50" s="31"/>
+      <c r="AB50" s="31"/>
       <c r="AC50" s="37"/>
     </row>
     <row r="51" spans="2:29" ht="15" customHeight="1">
-      <c r="B51" s="38"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
-      <c r="N51" s="32"/>
-      <c r="O51" s="32"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="32"/>
-      <c r="R51" s="32"/>
-      <c r="S51" s="32"/>
-      <c r="T51" s="32"/>
-      <c r="U51" s="32"/>
-      <c r="V51" s="32"/>
-      <c r="W51" s="32"/>
-      <c r="X51" s="32"/>
-      <c r="Y51" s="32"/>
-      <c r="Z51" s="32"/>
-      <c r="AA51" s="32"/>
-      <c r="AB51" s="32"/>
-      <c r="AC51" s="39"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="31"/>
+      <c r="S51" s="31"/>
+      <c r="T51" s="31"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="31"/>
+      <c r="W51" s="31"/>
+      <c r="X51" s="31"/>
+      <c r="Y51" s="31"/>
+      <c r="Z51" s="31"/>
+      <c r="AA51" s="31"/>
+      <c r="AB51" s="31"/>
+      <c r="AC51" s="37"/>
+    </row>
+    <row r="52" spans="2:29" ht="15" customHeight="1">
+      <c r="B52" s="36"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
+      <c r="S52" s="31"/>
+      <c r="T52" s="31"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="31"/>
+      <c r="W52" s="31"/>
+      <c r="X52" s="31"/>
+      <c r="Y52" s="31"/>
+      <c r="Z52" s="31"/>
+      <c r="AA52" s="31"/>
+      <c r="AB52" s="31"/>
+      <c r="AC52" s="37"/>
+    </row>
+    <row r="53" spans="2:29" ht="15" customHeight="1">
+      <c r="B53" s="36"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
+      <c r="P53" s="31"/>
+      <c r="Q53" s="31"/>
+      <c r="R53" s="31"/>
+      <c r="S53" s="31"/>
+      <c r="T53" s="31"/>
+      <c r="U53" s="31"/>
+      <c r="V53" s="31"/>
+      <c r="W53" s="31"/>
+      <c r="X53" s="31"/>
+      <c r="Y53" s="31"/>
+      <c r="Z53" s="31"/>
+      <c r="AA53" s="31"/>
+      <c r="AB53" s="31"/>
+      <c r="AC53" s="37"/>
+    </row>
+    <row r="54" spans="2:29" ht="15" customHeight="1">
+      <c r="B54" s="38"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="N54" s="32"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
+      <c r="V54" s="32"/>
+      <c r="W54" s="32"/>
+      <c r="X54" s="32"/>
+      <c r="Y54" s="32"/>
+      <c r="Z54" s="32"/>
+      <c r="AA54" s="32"/>
+      <c r="AB54" s="32"/>
+      <c r="AC54" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B42:AC43"/>
-    <mergeCell ref="B44:AC51"/>
     <mergeCell ref="B2:AC3"/>
     <mergeCell ref="B4:AC5"/>
     <mergeCell ref="B6:AC34"/>
     <mergeCell ref="B35:AC36"/>
-    <mergeCell ref="B37:AC41"/>
+    <mergeCell ref="B37:AC44"/>
+    <mergeCell ref="B45:AC46"/>
+    <mergeCell ref="B47:AC54"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="88" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3714,95 +3804,95 @@
       <c r="B2" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
     </row>
     <row r="3" spans="2:29" ht="15" customHeight="1">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
     </row>
     <row r="4" spans="2:29" ht="15" customHeight="1">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
     </row>
     <row r="5" spans="2:29" ht="15" customHeight="1">
       <c r="B5" s="32"/>
@@ -3866,842 +3956,842 @@
     </row>
     <row r="7" spans="2:29" ht="15" customHeight="1">
       <c r="B7" s="36"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
       <c r="AC7" s="37"/>
     </row>
     <row r="8" spans="2:29" ht="15" customHeight="1">
       <c r="B8" s="36"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
       <c r="AC8" s="37"/>
     </row>
     <row r="9" spans="2:29" ht="15" customHeight="1">
       <c r="B9" s="36"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
       <c r="AC9" s="37"/>
     </row>
     <row r="10" spans="2:29" ht="15" customHeight="1">
       <c r="B10" s="36"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
       <c r="AC10" s="37"/>
     </row>
     <row r="11" spans="2:29" ht="15" customHeight="1">
       <c r="B11" s="36"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
       <c r="AC11" s="37"/>
     </row>
     <row r="12" spans="2:29" ht="15" customHeight="1">
       <c r="B12" s="36"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
       <c r="AC12" s="37"/>
     </row>
     <row r="13" spans="2:29" ht="15" customHeight="1">
       <c r="B13" s="36"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
       <c r="AC13" s="37"/>
     </row>
     <row r="14" spans="2:29" ht="15" customHeight="1">
       <c r="B14" s="36"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
       <c r="AC14" s="37"/>
     </row>
     <row r="15" spans="2:29" ht="15" customHeight="1">
       <c r="B15" s="36"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31"/>
       <c r="AC15" s="37"/>
     </row>
     <row r="16" spans="2:29" ht="15" customHeight="1">
       <c r="B16" s="36"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
       <c r="AC16" s="37"/>
     </row>
     <row r="17" spans="2:29" ht="15" customHeight="1">
       <c r="B17" s="36"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
       <c r="AC17" s="37"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1">
       <c r="B18" s="36"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
       <c r="AC18" s="37"/>
     </row>
     <row r="19" spans="2:29" ht="15" customHeight="1">
       <c r="B19" s="36"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="31"/>
       <c r="AC19" s="37"/>
     </row>
     <row r="20" spans="2:29" ht="15" customHeight="1">
       <c r="B20" s="36"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
       <c r="AC20" s="37"/>
     </row>
     <row r="21" spans="2:29" ht="15" customHeight="1">
       <c r="B21" s="36"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="30"/>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
-      <c r="AA21" s="30"/>
-      <c r="AB21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="31"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="31"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="31"/>
+      <c r="AB21" s="31"/>
       <c r="AC21" s="37"/>
     </row>
     <row r="22" spans="2:29" ht="15" customHeight="1">
       <c r="B22" s="36"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
       <c r="AC22" s="37"/>
     </row>
     <row r="23" spans="2:29" ht="15" customHeight="1">
       <c r="B23" s="36"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
       <c r="AC23" s="37"/>
     </row>
     <row r="24" spans="2:29" ht="15" customHeight="1">
       <c r="B24" s="36"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="31"/>
       <c r="AC24" s="37"/>
     </row>
     <row r="25" spans="2:29" ht="15" customHeight="1">
       <c r="B25" s="36"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="31"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
       <c r="AC25" s="37"/>
     </row>
     <row r="26" spans="2:29" ht="15" customHeight="1">
       <c r="B26" s="36"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
       <c r="AC26" s="37"/>
     </row>
     <row r="27" spans="2:29" ht="15" customHeight="1">
       <c r="B27" s="36"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="31"/>
       <c r="AC27" s="37"/>
     </row>
     <row r="28" spans="2:29" ht="15" customHeight="1">
       <c r="B28" s="36"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
       <c r="AC28" s="37"/>
     </row>
     <row r="29" spans="2:29" ht="15" customHeight="1">
       <c r="B29" s="36"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
       <c r="AC29" s="37"/>
     </row>
     <row r="30" spans="2:29" ht="15" customHeight="1">
       <c r="B30" s="36"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="31"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
       <c r="AC30" s="37"/>
     </row>
     <row r="31" spans="2:29" ht="15" customHeight="1">
       <c r="B31" s="36"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
       <c r="AC31" s="37"/>
     </row>
     <row r="32" spans="2:29" ht="15" customHeight="1">
       <c r="B32" s="36"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
       <c r="AC32" s="37"/>
     </row>
     <row r="33" spans="2:29" ht="15" customHeight="1">
       <c r="B33" s="36"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="31"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="31"/>
+      <c r="AB33" s="31"/>
       <c r="AC33" s="37"/>
     </row>
     <row r="34" spans="2:29" ht="15" customHeight="1">
       <c r="B34" s="36"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
       <c r="AC34" s="37"/>
     </row>
     <row r="35" spans="2:29" ht="15" customHeight="1">
@@ -4735,36 +4825,36 @@
       <c r="AC35" s="39"/>
     </row>
     <row r="37" spans="2:29" ht="15" customHeight="1">
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
     </row>
     <row r="38" spans="2:29" ht="15" customHeight="1">
       <c r="B38" s="32"/>
@@ -4828,182 +4918,182 @@
     </row>
     <row r="40" spans="2:29" ht="15" customHeight="1">
       <c r="B40" s="36"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
       <c r="AC40" s="37"/>
     </row>
     <row r="41" spans="2:29" ht="15" customHeight="1">
       <c r="B41" s="36"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
-      <c r="R41" s="30"/>
-      <c r="S41" s="30"/>
-      <c r="T41" s="30"/>
-      <c r="U41" s="30"/>
-      <c r="V41" s="30"/>
-      <c r="W41" s="30"/>
-      <c r="X41" s="30"/>
-      <c r="Y41" s="30"/>
-      <c r="Z41" s="30"/>
-      <c r="AA41" s="30"/>
-      <c r="AB41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="31"/>
+      <c r="S41" s="31"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="31"/>
+      <c r="Y41" s="31"/>
+      <c r="Z41" s="31"/>
+      <c r="AA41" s="31"/>
+      <c r="AB41" s="31"/>
       <c r="AC41" s="37"/>
     </row>
     <row r="42" spans="2:29" ht="15" customHeight="1">
       <c r="B42" s="36"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
-      <c r="W42" s="30"/>
-      <c r="X42" s="30"/>
-      <c r="Y42" s="30"/>
-      <c r="Z42" s="30"/>
-      <c r="AA42" s="30"/>
-      <c r="AB42" s="30"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="31"/>
+      <c r="Y42" s="31"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
       <c r="AC42" s="37"/>
     </row>
     <row r="43" spans="2:29" ht="15" customHeight="1">
       <c r="B43" s="36"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
       <c r="AC43" s="37"/>
     </row>
     <row r="44" spans="2:29" ht="15" customHeight="1">
       <c r="B44" s="36"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="30"/>
-      <c r="S44" s="30"/>
-      <c r="T44" s="30"/>
-      <c r="U44" s="30"/>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
-      <c r="X44" s="30"/>
-      <c r="Y44" s="30"/>
-      <c r="Z44" s="30"/>
-      <c r="AA44" s="30"/>
-      <c r="AB44" s="30"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="31"/>
+      <c r="S44" s="31"/>
+      <c r="T44" s="31"/>
+      <c r="U44" s="31"/>
+      <c r="V44" s="31"/>
+      <c r="W44" s="31"/>
+      <c r="X44" s="31"/>
+      <c r="Y44" s="31"/>
+      <c r="Z44" s="31"/>
+      <c r="AA44" s="31"/>
+      <c r="AB44" s="31"/>
       <c r="AC44" s="37"/>
     </row>
     <row r="45" spans="2:29" ht="15" customHeight="1">
       <c r="B45" s="36"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="30"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
-      <c r="X45" s="30"/>
-      <c r="Y45" s="30"/>
-      <c r="Z45" s="30"/>
-      <c r="AA45" s="30"/>
-      <c r="AB45" s="30"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="31"/>
+      <c r="S45" s="31"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
+      <c r="W45" s="31"/>
+      <c r="X45" s="31"/>
+      <c r="Y45" s="31"/>
+      <c r="Z45" s="31"/>
+      <c r="AA45" s="31"/>
+      <c r="AB45" s="31"/>
       <c r="AC45" s="37"/>
     </row>
     <row r="46" spans="2:29" ht="15" customHeight="1">
